--- a/artfynd/A 38123-2024 artfynd.xlsx
+++ b/artfynd/A 38123-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515884</v>
+        <v>121515881</v>
       </c>
       <c r="B2" t="n">
         <v>57354</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593756</v>
+        <v>593763</v>
       </c>
       <c r="R2" t="n">
-        <v>7183462</v>
+        <v>7183466</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515891</v>
+        <v>121515889</v>
       </c>
       <c r="B3" t="n">
         <v>57354</v>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593657</v>
+        <v>593689</v>
       </c>
       <c r="R3" t="n">
-        <v>7183534</v>
+        <v>7183537</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515882</v>
+        <v>121515893</v>
       </c>
       <c r="B4" t="n">
         <v>57354</v>
@@ -945,7 +945,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593762</v>
+        <v>593618</v>
       </c>
       <c r="R4" t="n">
-        <v>7183468</v>
+        <v>7183571</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515889</v>
+        <v>121515883</v>
       </c>
       <c r="B5" t="n">
         <v>57354</v>
@@ -1062,7 +1062,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593689</v>
+        <v>593756</v>
       </c>
       <c r="R5" t="n">
-        <v>7183537</v>
+        <v>7183469</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515881</v>
+        <v>121515885</v>
       </c>
       <c r="B6" t="n">
         <v>57354</v>
@@ -1179,7 +1179,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593763</v>
+        <v>593747</v>
       </c>
       <c r="R6" t="n">
-        <v>7183466</v>
+        <v>7183470</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515919</v>
+        <v>121515888</v>
       </c>
       <c r="B7" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,34 +1276,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593574</v>
+        <v>593716</v>
       </c>
       <c r="R7" t="n">
-        <v>7183442</v>
+        <v>7183526</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1335,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515885</v>
+        <v>121515919</v>
       </c>
       <c r="B8" t="n">
-        <v>57354</v>
+        <v>78607</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,39 +1393,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593747</v>
+        <v>593574</v>
       </c>
       <c r="R8" t="n">
-        <v>7183470</v>
+        <v>7183442</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,7 +1489,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515890</v>
+        <v>121515891</v>
       </c>
       <c r="B9" t="n">
         <v>57354</v>
@@ -1525,7 +1525,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593688</v>
+        <v>593657</v>
       </c>
       <c r="R9" t="n">
-        <v>7183529</v>
+        <v>7183534</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,10 +1606,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515914</v>
+        <v>121515920</v>
       </c>
       <c r="B10" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,34 +1622,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593577</v>
+        <v>593492</v>
       </c>
       <c r="R10" t="n">
-        <v>7183447</v>
+        <v>7183248</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1681,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1696,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,7 +1723,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515883</v>
+        <v>121515892</v>
       </c>
       <c r="B11" t="n">
         <v>57354</v>
@@ -1754,7 +1759,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1763,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593756</v>
+        <v>593635</v>
       </c>
       <c r="R11" t="n">
-        <v>7183469</v>
+        <v>7183578</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1798,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1808,7 +1813,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,7 +1840,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515922</v>
+        <v>121515882</v>
       </c>
       <c r="B12" t="n">
         <v>57354</v>
@@ -1871,7 +1876,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1880,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593510</v>
+        <v>593762</v>
       </c>
       <c r="R12" t="n">
-        <v>7183224</v>
+        <v>7183468</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1915,7 +1920,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1930,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,7 +1957,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515888</v>
+        <v>121515922</v>
       </c>
       <c r="B13" t="n">
         <v>57354</v>
@@ -1988,7 +1993,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1997,10 +2002,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593716</v>
+        <v>593510</v>
       </c>
       <c r="R13" t="n">
-        <v>7183526</v>
+        <v>7183224</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2032,7 +2037,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2042,7 +2047,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2069,10 +2074,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515892</v>
+        <v>121515918</v>
       </c>
       <c r="B14" t="n">
-        <v>57354</v>
+        <v>57370</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2085,16 +2090,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2105,7 +2110,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2114,10 +2119,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593635</v>
+        <v>593574</v>
       </c>
       <c r="R14" t="n">
-        <v>7183578</v>
+        <v>7183444</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2149,7 +2154,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2159,7 +2164,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2186,7 +2191,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515920</v>
+        <v>121515890</v>
       </c>
       <c r="B15" t="n">
         <v>57354</v>
@@ -2231,10 +2236,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593492</v>
+        <v>593688</v>
       </c>
       <c r="R15" t="n">
-        <v>7183248</v>
+        <v>7183529</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2266,7 +2271,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2276,7 +2281,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2303,7 +2308,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515893</v>
+        <v>121515884</v>
       </c>
       <c r="B16" t="n">
         <v>57354</v>
@@ -2339,7 +2344,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2348,10 +2353,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593618</v>
+        <v>593756</v>
       </c>
       <c r="R16" t="n">
-        <v>7183571</v>
+        <v>7183462</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2383,7 +2388,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2393,7 +2398,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2420,10 +2425,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515918</v>
+        <v>121515914</v>
       </c>
       <c r="B17" t="n">
-        <v>57370</v>
+        <v>78607</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2436,39 +2441,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593574</v>
+        <v>593577</v>
       </c>
       <c r="R17" t="n">
-        <v>7183444</v>
+        <v>7183447</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 38123-2024 artfynd.xlsx
+++ b/artfynd/A 38123-2024 artfynd.xlsx
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515893</v>
+        <v>121515883</v>
       </c>
       <c r="B4" t="n">
         <v>57354</v>
@@ -945,7 +945,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593618</v>
+        <v>593756</v>
       </c>
       <c r="R4" t="n">
-        <v>7183571</v>
+        <v>7183469</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515883</v>
+        <v>121515893</v>
       </c>
       <c r="B5" t="n">
         <v>57354</v>
@@ -1062,7 +1062,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593756</v>
+        <v>593618</v>
       </c>
       <c r="R5" t="n">
-        <v>7183469</v>
+        <v>7183571</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 38123-2024 artfynd.xlsx
+++ b/artfynd/A 38123-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515881</v>
+        <v>121515883</v>
       </c>
       <c r="B2" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593763</v>
+        <v>593756</v>
       </c>
       <c r="R2" t="n">
-        <v>7183466</v>
+        <v>7183469</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515889</v>
+        <v>121515922</v>
       </c>
       <c r="B3" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593689</v>
+        <v>593510</v>
       </c>
       <c r="R3" t="n">
-        <v>7183537</v>
+        <v>7183224</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515883</v>
+        <v>121515892</v>
       </c>
       <c r="B4" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593756</v>
+        <v>593635</v>
       </c>
       <c r="R4" t="n">
-        <v>7183469</v>
+        <v>7183578</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515893</v>
+        <v>121515919</v>
       </c>
       <c r="B5" t="n">
-        <v>57354</v>
+        <v>78608</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,39 +1042,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593618</v>
+        <v>593574</v>
       </c>
       <c r="R5" t="n">
-        <v>7183571</v>
+        <v>7183442</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1106,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515885</v>
+        <v>121515918</v>
       </c>
       <c r="B6" t="n">
-        <v>57354</v>
+        <v>57371</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,16 +1154,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1179,7 +1174,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1188,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593747</v>
+        <v>593574</v>
       </c>
       <c r="R6" t="n">
-        <v>7183470</v>
+        <v>7183444</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1223,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515888</v>
+        <v>121515914</v>
       </c>
       <c r="B7" t="n">
-        <v>57354</v>
+        <v>78608</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,39 +1271,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593716</v>
+        <v>593577</v>
       </c>
       <c r="R7" t="n">
-        <v>7183526</v>
+        <v>7183447</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1340,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515919</v>
+        <v>121515881</v>
       </c>
       <c r="B8" t="n">
-        <v>78607</v>
+        <v>57355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,34 +1383,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593574</v>
+        <v>593763</v>
       </c>
       <c r="R8" t="n">
-        <v>7183442</v>
+        <v>7183466</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1452,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515891</v>
+        <v>121515920</v>
       </c>
       <c r="B9" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1525,7 +1520,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1534,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593657</v>
+        <v>593492</v>
       </c>
       <c r="R9" t="n">
-        <v>7183534</v>
+        <v>7183248</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1569,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515920</v>
+        <v>121515884</v>
       </c>
       <c r="B10" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1651,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593492</v>
+        <v>593756</v>
       </c>
       <c r="R10" t="n">
-        <v>7183248</v>
+        <v>7183462</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1686,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,7 +1691,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1723,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515892</v>
+        <v>121515890</v>
       </c>
       <c r="B11" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1759,7 +1754,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1768,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593635</v>
+        <v>593688</v>
       </c>
       <c r="R11" t="n">
-        <v>7183578</v>
+        <v>7183529</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1803,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,7 +1808,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,10 +1835,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515882</v>
+        <v>121515889</v>
       </c>
       <c r="B12" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1876,7 +1871,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1885,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593762</v>
+        <v>593689</v>
       </c>
       <c r="R12" t="n">
-        <v>7183468</v>
+        <v>7183537</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1920,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1930,7 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,10 +1952,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515922</v>
+        <v>121515885</v>
       </c>
       <c r="B13" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2002,10 +1997,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593510</v>
+        <v>593747</v>
       </c>
       <c r="R13" t="n">
-        <v>7183224</v>
+        <v>7183470</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2037,7 +2032,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2047,7 +2042,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,10 +2069,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515918</v>
+        <v>121515882</v>
       </c>
       <c r="B14" t="n">
-        <v>57370</v>
+        <v>57355</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2090,16 +2085,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2119,10 +2114,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593574</v>
+        <v>593762</v>
       </c>
       <c r="R14" t="n">
-        <v>7183444</v>
+        <v>7183468</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2154,7 +2149,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2164,7 +2159,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2191,10 +2186,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515890</v>
+        <v>121515888</v>
       </c>
       <c r="B15" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2236,10 +2231,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593688</v>
+        <v>593716</v>
       </c>
       <c r="R15" t="n">
-        <v>7183529</v>
+        <v>7183526</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2271,7 +2266,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2281,7 +2276,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2308,10 +2303,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515884</v>
+        <v>121515891</v>
       </c>
       <c r="B16" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2344,7 +2339,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2353,10 +2348,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593756</v>
+        <v>593657</v>
       </c>
       <c r="R16" t="n">
-        <v>7183462</v>
+        <v>7183534</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2388,7 +2383,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2398,7 +2393,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2425,10 +2420,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515914</v>
+        <v>121515893</v>
       </c>
       <c r="B17" t="n">
-        <v>78607</v>
+        <v>57355</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2441,34 +2436,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593577</v>
+        <v>593618</v>
       </c>
       <c r="R17" t="n">
-        <v>7183447</v>
+        <v>7183571</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 38123-2024 artfynd.xlsx
+++ b/artfynd/A 38123-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515883</v>
+        <v>121515918</v>
       </c>
       <c r="B2" t="n">
-        <v>57355</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593756</v>
+        <v>593574</v>
       </c>
       <c r="R2" t="n">
-        <v>7183469</v>
+        <v>7183444</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515922</v>
+        <v>121515883</v>
       </c>
       <c r="B3" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593510</v>
+        <v>593756</v>
       </c>
       <c r="R3" t="n">
-        <v>7183224</v>
+        <v>7183469</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515892</v>
+        <v>121515885</v>
       </c>
       <c r="B4" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593635</v>
+        <v>593747</v>
       </c>
       <c r="R4" t="n">
-        <v>7183578</v>
+        <v>7183470</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515919</v>
+        <v>121515889</v>
       </c>
       <c r="B5" t="n">
-        <v>78608</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,34 +1042,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593574</v>
+        <v>593689</v>
       </c>
       <c r="R5" t="n">
-        <v>7183442</v>
+        <v>7183537</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515918</v>
+        <v>121515881</v>
       </c>
       <c r="B6" t="n">
-        <v>57371</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,16 +1159,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1183,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593574</v>
+        <v>593763</v>
       </c>
       <c r="R6" t="n">
-        <v>7183444</v>
+        <v>7183466</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1218,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515914</v>
+        <v>121515882</v>
       </c>
       <c r="B7" t="n">
-        <v>78608</v>
+        <v>57356</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,34 +1276,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593577</v>
+        <v>593762</v>
       </c>
       <c r="R7" t="n">
-        <v>7183447</v>
+        <v>7183468</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1330,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515881</v>
+        <v>121515914</v>
       </c>
       <c r="B8" t="n">
-        <v>57355</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,39 +1393,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593763</v>
+        <v>593577</v>
       </c>
       <c r="R8" t="n">
-        <v>7183466</v>
+        <v>7183447</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1447,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515920</v>
+        <v>121515919</v>
       </c>
       <c r="B9" t="n">
-        <v>57355</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,39 +1505,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593492</v>
+        <v>593574</v>
       </c>
       <c r="R9" t="n">
-        <v>7183248</v>
+        <v>7183442</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515884</v>
+        <v>121515891</v>
       </c>
       <c r="B10" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593756</v>
+        <v>593657</v>
       </c>
       <c r="R10" t="n">
-        <v>7183462</v>
+        <v>7183534</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515890</v>
+        <v>121515892</v>
       </c>
       <c r="B11" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593688</v>
+        <v>593635</v>
       </c>
       <c r="R11" t="n">
-        <v>7183529</v>
+        <v>7183578</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,10 +1835,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515889</v>
+        <v>121515893</v>
       </c>
       <c r="B12" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593689</v>
+        <v>593618</v>
       </c>
       <c r="R12" t="n">
-        <v>7183537</v>
+        <v>7183571</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,10 +1952,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515885</v>
+        <v>121515922</v>
       </c>
       <c r="B13" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593747</v>
+        <v>593510</v>
       </c>
       <c r="R13" t="n">
-        <v>7183470</v>
+        <v>7183224</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2069,10 +2069,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515882</v>
+        <v>121515884</v>
       </c>
       <c r="B14" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593762</v>
+        <v>593756</v>
       </c>
       <c r="R14" t="n">
-        <v>7183468</v>
+        <v>7183462</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2189,7 +2189,7 @@
         <v>121515888</v>
       </c>
       <c r="B15" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2303,10 +2303,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515891</v>
+        <v>121515920</v>
       </c>
       <c r="B16" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593657</v>
+        <v>593492</v>
       </c>
       <c r="R16" t="n">
-        <v>7183534</v>
+        <v>7183248</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2420,10 +2420,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515893</v>
+        <v>121515890</v>
       </c>
       <c r="B17" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593618</v>
+        <v>593688</v>
       </c>
       <c r="R17" t="n">
-        <v>7183571</v>
+        <v>7183529</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 38123-2024 artfynd.xlsx
+++ b/artfynd/A 38123-2024 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515883</v>
+        <v>121515914</v>
       </c>
       <c r="B3" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,39 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593756</v>
+        <v>593577</v>
       </c>
       <c r="R3" t="n">
-        <v>7183469</v>
+        <v>7183447</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515885</v>
+        <v>121515881</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -945,7 +940,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593747</v>
+        <v>593763</v>
       </c>
       <c r="R4" t="n">
-        <v>7183470</v>
+        <v>7183466</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -989,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515889</v>
+        <v>121515892</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1071,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593689</v>
+        <v>593635</v>
       </c>
       <c r="R5" t="n">
-        <v>7183537</v>
+        <v>7183578</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1106,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,7 +1138,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515881</v>
+        <v>121515883</v>
       </c>
       <c r="B6" t="n">
         <v>57356</v>
@@ -1188,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593763</v>
+        <v>593756</v>
       </c>
       <c r="R6" t="n">
-        <v>7183466</v>
+        <v>7183469</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1260,7 +1255,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515882</v>
+        <v>121515890</v>
       </c>
       <c r="B7" t="n">
         <v>57356</v>
@@ -1305,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593762</v>
+        <v>593688</v>
       </c>
       <c r="R7" t="n">
-        <v>7183468</v>
+        <v>7183529</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1340,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,7 +1345,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515914</v>
+        <v>121515889</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,34 +1388,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593577</v>
+        <v>593689</v>
       </c>
       <c r="R8" t="n">
-        <v>7183447</v>
+        <v>7183537</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515919</v>
+        <v>121515920</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,34 +1505,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593574</v>
+        <v>593492</v>
       </c>
       <c r="R9" t="n">
-        <v>7183442</v>
+        <v>7183248</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1564,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1579,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1718,10 +1723,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515892</v>
+        <v>121515919</v>
       </c>
       <c r="B11" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,39 +1739,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593635</v>
+        <v>593574</v>
       </c>
       <c r="R11" t="n">
-        <v>7183578</v>
+        <v>7183442</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,7 +1835,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515893</v>
+        <v>121515884</v>
       </c>
       <c r="B12" t="n">
         <v>57356</v>
@@ -1871,7 +1871,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593618</v>
+        <v>593756</v>
       </c>
       <c r="R12" t="n">
-        <v>7183571</v>
+        <v>7183462</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,7 +1952,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515922</v>
+        <v>121515885</v>
       </c>
       <c r="B13" t="n">
         <v>57356</v>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593510</v>
+        <v>593747</v>
       </c>
       <c r="R13" t="n">
-        <v>7183224</v>
+        <v>7183470</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2069,7 +2069,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515884</v>
+        <v>121515922</v>
       </c>
       <c r="B14" t="n">
         <v>57356</v>
@@ -2105,7 +2105,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593756</v>
+        <v>593510</v>
       </c>
       <c r="R14" t="n">
-        <v>7183462</v>
+        <v>7183224</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2186,7 +2186,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515888</v>
+        <v>121515893</v>
       </c>
       <c r="B15" t="n">
         <v>57356</v>
@@ -2222,7 +2222,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593716</v>
+        <v>593618</v>
       </c>
       <c r="R15" t="n">
-        <v>7183526</v>
+        <v>7183571</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2303,7 +2303,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515920</v>
+        <v>121515882</v>
       </c>
       <c r="B16" t="n">
         <v>57356</v>
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593492</v>
+        <v>593762</v>
       </c>
       <c r="R16" t="n">
-        <v>7183248</v>
+        <v>7183468</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2420,7 +2420,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515890</v>
+        <v>121515888</v>
       </c>
       <c r="B17" t="n">
         <v>57356</v>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593688</v>
+        <v>593716</v>
       </c>
       <c r="R17" t="n">
-        <v>7183529</v>
+        <v>7183526</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 38123-2024 artfynd.xlsx
+++ b/artfynd/A 38123-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515918</v>
+        <v>121515885</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593574</v>
+        <v>593747</v>
       </c>
       <c r="R2" t="n">
-        <v>7183444</v>
+        <v>7183470</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515914</v>
+        <v>121515889</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +808,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593577</v>
+        <v>593689</v>
       </c>
       <c r="R3" t="n">
-        <v>7183447</v>
+        <v>7183537</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515881</v>
+        <v>121515919</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,39 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593763</v>
+        <v>593574</v>
       </c>
       <c r="R4" t="n">
-        <v>7183466</v>
+        <v>7183442</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515892</v>
+        <v>121515922</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593635</v>
+        <v>593510</v>
       </c>
       <c r="R5" t="n">
-        <v>7183578</v>
+        <v>7183224</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1372,7 +1372,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515889</v>
+        <v>121515891</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593689</v>
+        <v>593657</v>
       </c>
       <c r="R8" t="n">
-        <v>7183537</v>
+        <v>7183534</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1606,7 +1606,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515891</v>
+        <v>121515888</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1642,7 +1642,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593657</v>
+        <v>593716</v>
       </c>
       <c r="R10" t="n">
-        <v>7183534</v>
+        <v>7183526</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1723,7 +1723,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515919</v>
+        <v>121515914</v>
       </c>
       <c r="B11" t="n">
         <v>78609</v>
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593574</v>
+        <v>593577</v>
       </c>
       <c r="R11" t="n">
-        <v>7183442</v>
+        <v>7183447</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,7 +1835,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515884</v>
+        <v>121515892</v>
       </c>
       <c r="B12" t="n">
         <v>57356</v>
@@ -1871,7 +1871,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593756</v>
+        <v>593635</v>
       </c>
       <c r="R12" t="n">
-        <v>7183462</v>
+        <v>7183578</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,10 +1952,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515885</v>
+        <v>121515918</v>
       </c>
       <c r="B13" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1968,16 +1968,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1988,7 +1988,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593747</v>
+        <v>593574</v>
       </c>
       <c r="R13" t="n">
-        <v>7183470</v>
+        <v>7183444</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2069,7 +2069,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515922</v>
+        <v>121515881</v>
       </c>
       <c r="B14" t="n">
         <v>57356</v>
@@ -2105,7 +2105,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593510</v>
+        <v>593763</v>
       </c>
       <c r="R14" t="n">
-        <v>7183224</v>
+        <v>7183466</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2186,7 +2186,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515893</v>
+        <v>121515882</v>
       </c>
       <c r="B15" t="n">
         <v>57356</v>
@@ -2222,7 +2222,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593618</v>
+        <v>593762</v>
       </c>
       <c r="R15" t="n">
-        <v>7183571</v>
+        <v>7183468</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2303,7 +2303,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515882</v>
+        <v>121515893</v>
       </c>
       <c r="B16" t="n">
         <v>57356</v>
@@ -2339,7 +2339,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593762</v>
+        <v>593618</v>
       </c>
       <c r="R16" t="n">
-        <v>7183468</v>
+        <v>7183571</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2420,7 +2420,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515888</v>
+        <v>121515884</v>
       </c>
       <c r="B17" t="n">
         <v>57356</v>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593716</v>
+        <v>593756</v>
       </c>
       <c r="R17" t="n">
-        <v>7183526</v>
+        <v>7183462</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 38123-2024 artfynd.xlsx
+++ b/artfynd/A 38123-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515885</v>
+        <v>121515882</v>
       </c>
       <c r="B2" t="n">
         <v>57356</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593747</v>
+        <v>593762</v>
       </c>
       <c r="R2" t="n">
-        <v>7183470</v>
+        <v>7183468</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515889</v>
+        <v>121515890</v>
       </c>
       <c r="B3" t="n">
         <v>57356</v>
@@ -828,7 +828,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593689</v>
+        <v>593688</v>
       </c>
       <c r="R3" t="n">
-        <v>7183537</v>
+        <v>7183529</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515919</v>
+        <v>121515885</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,34 +925,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593574</v>
+        <v>593747</v>
       </c>
       <c r="R4" t="n">
-        <v>7183442</v>
+        <v>7183470</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515922</v>
+        <v>121515889</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1066,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593510</v>
+        <v>593689</v>
       </c>
       <c r="R5" t="n">
-        <v>7183224</v>
+        <v>7183537</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515883</v>
+        <v>121515920</v>
       </c>
       <c r="B6" t="n">
         <v>57356</v>
@@ -1183,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593756</v>
+        <v>593492</v>
       </c>
       <c r="R6" t="n">
-        <v>7183469</v>
+        <v>7183248</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1218,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,7 +1260,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515890</v>
+        <v>121515922</v>
       </c>
       <c r="B7" t="n">
         <v>57356</v>
@@ -1291,7 +1296,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1300,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593688</v>
+        <v>593510</v>
       </c>
       <c r="R7" t="n">
-        <v>7183529</v>
+        <v>7183224</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1335,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515891</v>
+        <v>121515919</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,39 +1393,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593657</v>
+        <v>593574</v>
       </c>
       <c r="R8" t="n">
-        <v>7183534</v>
+        <v>7183442</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515920</v>
+        <v>121515914</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,39 +1505,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593492</v>
+        <v>593577</v>
       </c>
       <c r="R9" t="n">
-        <v>7183248</v>
+        <v>7183447</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1569,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,7 +1601,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515888</v>
+        <v>121515893</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1642,7 +1637,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1651,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593716</v>
+        <v>593618</v>
       </c>
       <c r="R10" t="n">
-        <v>7183526</v>
+        <v>7183571</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1686,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,7 +1691,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1723,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515914</v>
+        <v>121515888</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1739,34 +1734,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593577</v>
+        <v>593716</v>
       </c>
       <c r="R11" t="n">
-        <v>7183447</v>
+        <v>7183526</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,7 +1835,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515892</v>
+        <v>121515883</v>
       </c>
       <c r="B12" t="n">
         <v>57356</v>
@@ -1871,7 +1871,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593635</v>
+        <v>593756</v>
       </c>
       <c r="R12" t="n">
-        <v>7183578</v>
+        <v>7183469</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,10 +1952,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515918</v>
+        <v>121515891</v>
       </c>
       <c r="B13" t="n">
-        <v>57372</v>
+        <v>57356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1968,16 +1968,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1988,7 +1988,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593574</v>
+        <v>593657</v>
       </c>
       <c r="R13" t="n">
-        <v>7183444</v>
+        <v>7183534</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2069,7 +2069,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515881</v>
+        <v>121515892</v>
       </c>
       <c r="B14" t="n">
         <v>57356</v>
@@ -2105,7 +2105,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593763</v>
+        <v>593635</v>
       </c>
       <c r="R14" t="n">
-        <v>7183466</v>
+        <v>7183578</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2186,10 +2186,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515882</v>
+        <v>121515918</v>
       </c>
       <c r="B15" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2202,16 +2202,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593762</v>
+        <v>593574</v>
       </c>
       <c r="R15" t="n">
-        <v>7183468</v>
+        <v>7183444</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2303,7 +2303,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515893</v>
+        <v>121515884</v>
       </c>
       <c r="B16" t="n">
         <v>57356</v>
@@ -2339,7 +2339,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593618</v>
+        <v>593756</v>
       </c>
       <c r="R16" t="n">
-        <v>7183571</v>
+        <v>7183462</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2420,7 +2420,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515884</v>
+        <v>121515881</v>
       </c>
       <c r="B17" t="n">
         <v>57356</v>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593756</v>
+        <v>593763</v>
       </c>
       <c r="R17" t="n">
-        <v>7183462</v>
+        <v>7183466</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 38123-2024 artfynd.xlsx
+++ b/artfynd/A 38123-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515885</v>
+        <v>121515889</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593747</v>
+        <v>593689</v>
       </c>
       <c r="R2" t="n">
-        <v>7183470</v>
+        <v>7183537</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515919</v>
+        <v>121515920</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +808,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593574</v>
+        <v>593492</v>
       </c>
       <c r="R3" t="n">
-        <v>7183442</v>
+        <v>7183248</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515882</v>
+        <v>121515883</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -949,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593762</v>
+        <v>593756</v>
       </c>
       <c r="R4" t="n">
-        <v>7183468</v>
+        <v>7183469</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1138,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515884</v>
+        <v>121515892</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1174,7 +1179,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1183,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593756</v>
+        <v>593635</v>
       </c>
       <c r="R6" t="n">
-        <v>7183462</v>
+        <v>7183578</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1218,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515892</v>
+        <v>121515918</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,16 +1276,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1291,7 +1296,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1300,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593635</v>
+        <v>593574</v>
       </c>
       <c r="R7" t="n">
-        <v>7183578</v>
+        <v>7183444</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1335,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,7 +1377,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515893</v>
+        <v>121515888</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1408,7 +1413,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1417,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593618</v>
+        <v>593716</v>
       </c>
       <c r="R8" t="n">
-        <v>7183571</v>
+        <v>7183526</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1452,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,7 +1494,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515888</v>
+        <v>121515885</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1525,7 +1530,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1534,10 +1539,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593716</v>
+        <v>593747</v>
       </c>
       <c r="R9" t="n">
-        <v>7183526</v>
+        <v>7183470</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1569,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,7 +1584,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515918</v>
+        <v>121515922</v>
       </c>
       <c r="B10" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,16 +1627,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1642,7 +1647,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1651,10 +1656,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593574</v>
+        <v>593510</v>
       </c>
       <c r="R10" t="n">
-        <v>7183444</v>
+        <v>7183224</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1686,7 +1691,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,7 +1701,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1723,7 +1728,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515922</v>
+        <v>121515882</v>
       </c>
       <c r="B11" t="n">
         <v>57357</v>
@@ -1759,7 +1764,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1768,10 +1773,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593510</v>
+        <v>593762</v>
       </c>
       <c r="R11" t="n">
-        <v>7183224</v>
+        <v>7183468</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1803,7 +1808,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,7 +1818,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,7 +1845,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515881</v>
+        <v>121515890</v>
       </c>
       <c r="B12" t="n">
         <v>57357</v>
@@ -1885,10 +1890,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593763</v>
+        <v>593688</v>
       </c>
       <c r="R12" t="n">
-        <v>7183466</v>
+        <v>7183529</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1920,7 +1925,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1930,7 +1935,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515920</v>
+        <v>121515919</v>
       </c>
       <c r="B13" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1973,39 +1978,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593492</v>
+        <v>593574</v>
       </c>
       <c r="R13" t="n">
-        <v>7183248</v>
+        <v>7183442</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2186,7 +2186,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515890</v>
+        <v>121515881</v>
       </c>
       <c r="B15" t="n">
         <v>57357</v>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593688</v>
+        <v>593763</v>
       </c>
       <c r="R15" t="n">
-        <v>7183529</v>
+        <v>7183466</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2303,7 +2303,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515889</v>
+        <v>121515893</v>
       </c>
       <c r="B16" t="n">
         <v>57357</v>
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593689</v>
+        <v>593618</v>
       </c>
       <c r="R16" t="n">
-        <v>7183537</v>
+        <v>7183571</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2420,7 +2420,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515883</v>
+        <v>121515884</v>
       </c>
       <c r="B17" t="n">
         <v>57357</v>
@@ -2468,7 +2468,7 @@
         <v>593756</v>
       </c>
       <c r="R17" t="n">
-        <v>7183469</v>
+        <v>7183462</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 38123-2024 artfynd.xlsx
+++ b/artfynd/A 38123-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515889</v>
+        <v>121515890</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593689</v>
+        <v>593688</v>
       </c>
       <c r="R2" t="n">
-        <v>7183537</v>
+        <v>7183529</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515920</v>
+        <v>121515883</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593492</v>
+        <v>593756</v>
       </c>
       <c r="R3" t="n">
-        <v>7183248</v>
+        <v>7183469</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515883</v>
+        <v>121515881</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593756</v>
+        <v>593763</v>
       </c>
       <c r="R4" t="n">
-        <v>7183469</v>
+        <v>7183466</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515891</v>
+        <v>121515892</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593657</v>
+        <v>593635</v>
       </c>
       <c r="R5" t="n">
-        <v>7183534</v>
+        <v>7183578</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515892</v>
+        <v>121515888</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1179,7 +1179,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593635</v>
+        <v>593716</v>
       </c>
       <c r="R6" t="n">
-        <v>7183578</v>
+        <v>7183526</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515918</v>
+        <v>121515922</v>
       </c>
       <c r="B7" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,16 +1276,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1296,7 +1296,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593574</v>
+        <v>593510</v>
       </c>
       <c r="R7" t="n">
-        <v>7183444</v>
+        <v>7183224</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515888</v>
+        <v>121515918</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,16 +1393,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593716</v>
+        <v>593574</v>
       </c>
       <c r="R8" t="n">
-        <v>7183526</v>
+        <v>7183444</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,7 +1494,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515885</v>
+        <v>121515891</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593747</v>
+        <v>593657</v>
       </c>
       <c r="R9" t="n">
-        <v>7183470</v>
+        <v>7183534</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,7 +1611,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515922</v>
+        <v>121515882</v>
       </c>
       <c r="B10" t="n">
         <v>57357</v>
@@ -1647,7 +1647,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593510</v>
+        <v>593762</v>
       </c>
       <c r="R10" t="n">
-        <v>7183224</v>
+        <v>7183468</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515882</v>
+        <v>121515914</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,39 +1744,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593762</v>
+        <v>593577</v>
       </c>
       <c r="R11" t="n">
-        <v>7183468</v>
+        <v>7183447</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1808,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1818,7 +1813,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1845,7 +1840,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515890</v>
+        <v>121515920</v>
       </c>
       <c r="B12" t="n">
         <v>57357</v>
@@ -1890,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593688</v>
+        <v>593492</v>
       </c>
       <c r="R12" t="n">
-        <v>7183529</v>
+        <v>7183248</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1925,7 +1920,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1935,7 +1930,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1962,10 +1957,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515919</v>
+        <v>121515884</v>
       </c>
       <c r="B13" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1978,34 +1973,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593574</v>
+        <v>593756</v>
       </c>
       <c r="R13" t="n">
-        <v>7183442</v>
+        <v>7183462</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,7 +2074,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515914</v>
+        <v>121515919</v>
       </c>
       <c r="B14" t="n">
         <v>78616</v>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593577</v>
+        <v>593574</v>
       </c>
       <c r="R14" t="n">
-        <v>7183447</v>
+        <v>7183442</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2186,7 +2186,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515881</v>
+        <v>121515889</v>
       </c>
       <c r="B15" t="n">
         <v>57357</v>
@@ -2222,7 +2222,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593763</v>
+        <v>593689</v>
       </c>
       <c r="R15" t="n">
-        <v>7183466</v>
+        <v>7183537</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2303,7 +2303,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515893</v>
+        <v>121515885</v>
       </c>
       <c r="B16" t="n">
         <v>57357</v>
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593618</v>
+        <v>593747</v>
       </c>
       <c r="R16" t="n">
-        <v>7183571</v>
+        <v>7183470</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2420,7 +2420,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515884</v>
+        <v>121515893</v>
       </c>
       <c r="B17" t="n">
         <v>57357</v>
@@ -2456,7 +2456,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593756</v>
+        <v>593618</v>
       </c>
       <c r="R17" t="n">
-        <v>7183462</v>
+        <v>7183571</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 38123-2024 artfynd.xlsx
+++ b/artfynd/A 38123-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515890</v>
+        <v>121515881</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593688</v>
+        <v>593763</v>
       </c>
       <c r="R2" t="n">
-        <v>7183529</v>
+        <v>7183466</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515883</v>
+        <v>121515914</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,39 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593756</v>
+        <v>593577</v>
       </c>
       <c r="R3" t="n">
-        <v>7183469</v>
+        <v>7183447</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515881</v>
+        <v>121515888</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -954,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593763</v>
+        <v>593716</v>
       </c>
       <c r="R4" t="n">
-        <v>7183466</v>
+        <v>7183526</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -989,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515892</v>
+        <v>121515922</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1071,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593635</v>
+        <v>593510</v>
       </c>
       <c r="R5" t="n">
-        <v>7183578</v>
+        <v>7183224</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1106,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515888</v>
+        <v>121515918</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,16 +1154,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1188,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593716</v>
+        <v>593574</v>
       </c>
       <c r="R6" t="n">
-        <v>7183526</v>
+        <v>7183444</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1223,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,7 +1255,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515922</v>
+        <v>121515884</v>
       </c>
       <c r="B7" t="n">
         <v>57357</v>
@@ -1296,7 +1291,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1305,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593510</v>
+        <v>593756</v>
       </c>
       <c r="R7" t="n">
-        <v>7183224</v>
+        <v>7183462</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1340,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,7 +1345,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515918</v>
+        <v>121515882</v>
       </c>
       <c r="B8" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,16 +1388,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1422,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593574</v>
+        <v>593762</v>
       </c>
       <c r="R8" t="n">
-        <v>7183444</v>
+        <v>7183468</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1457,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,7 +1489,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515891</v>
+        <v>121515892</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1539,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593657</v>
+        <v>593635</v>
       </c>
       <c r="R9" t="n">
-        <v>7183534</v>
+        <v>7183578</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1574,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1579,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,7 +1606,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515882</v>
+        <v>121515889</v>
       </c>
       <c r="B10" t="n">
         <v>57357</v>
@@ -1647,7 +1642,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1656,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593762</v>
+        <v>593689</v>
       </c>
       <c r="R10" t="n">
-        <v>7183468</v>
+        <v>7183537</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1691,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,7 +1696,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,10 +1723,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515914</v>
+        <v>121515890</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,34 +1739,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593577</v>
+        <v>593688</v>
       </c>
       <c r="R11" t="n">
-        <v>7183447</v>
+        <v>7183529</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,7 +1840,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515920</v>
+        <v>121515885</v>
       </c>
       <c r="B12" t="n">
         <v>57357</v>
@@ -1876,7 +1876,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593492</v>
+        <v>593747</v>
       </c>
       <c r="R12" t="n">
-        <v>7183248</v>
+        <v>7183470</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,7 +1957,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515884</v>
+        <v>121515891</v>
       </c>
       <c r="B13" t="n">
         <v>57357</v>
@@ -1993,7 +1993,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593756</v>
+        <v>593657</v>
       </c>
       <c r="R13" t="n">
-        <v>7183462</v>
+        <v>7183534</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,10 +2074,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515919</v>
+        <v>121515893</v>
       </c>
       <c r="B14" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2090,34 +2090,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593574</v>
+        <v>593618</v>
       </c>
       <c r="R14" t="n">
-        <v>7183442</v>
+        <v>7183571</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2149,7 +2154,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2159,7 +2164,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2186,7 +2191,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515889</v>
+        <v>121515920</v>
       </c>
       <c r="B15" t="n">
         <v>57357</v>
@@ -2222,7 +2227,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2231,10 +2236,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593689</v>
+        <v>593492</v>
       </c>
       <c r="R15" t="n">
-        <v>7183537</v>
+        <v>7183248</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2266,7 +2271,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2276,7 +2281,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2303,10 +2308,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515885</v>
+        <v>121515919</v>
       </c>
       <c r="B16" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2319,39 +2324,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593747</v>
+        <v>593574</v>
       </c>
       <c r="R16" t="n">
-        <v>7183470</v>
+        <v>7183442</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2420,7 +2420,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515893</v>
+        <v>121515883</v>
       </c>
       <c r="B17" t="n">
         <v>57357</v>
@@ -2456,7 +2456,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593618</v>
+        <v>593756</v>
       </c>
       <c r="R17" t="n">
-        <v>7183571</v>
+        <v>7183469</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 38123-2024 artfynd.xlsx
+++ b/artfynd/A 38123-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515881</v>
+        <v>121515889</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593763</v>
+        <v>593689</v>
       </c>
       <c r="R2" t="n">
-        <v>7183466</v>
+        <v>7183537</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515914</v>
+        <v>121515919</v>
       </c>
       <c r="B3" t="n">
         <v>78616</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593577</v>
+        <v>593574</v>
       </c>
       <c r="R3" t="n">
-        <v>7183447</v>
+        <v>7183442</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1021,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515922</v>
+        <v>121515881</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1057,7 +1057,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593510</v>
+        <v>593763</v>
       </c>
       <c r="R5" t="n">
-        <v>7183224</v>
+        <v>7183466</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515918</v>
+        <v>121515885</v>
       </c>
       <c r="B6" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,16 +1154,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1174,7 +1174,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593574</v>
+        <v>593747</v>
       </c>
       <c r="R6" t="n">
-        <v>7183444</v>
+        <v>7183470</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1372,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515882</v>
+        <v>121515914</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,39 +1388,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593762</v>
+        <v>593577</v>
       </c>
       <c r="R8" t="n">
-        <v>7183468</v>
+        <v>7183447</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1452,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,7 +1484,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515892</v>
+        <v>121515883</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1525,7 +1520,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1534,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593635</v>
+        <v>593756</v>
       </c>
       <c r="R9" t="n">
-        <v>7183578</v>
+        <v>7183469</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1569,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,7 +1601,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515889</v>
+        <v>121515890</v>
       </c>
       <c r="B10" t="n">
         <v>57357</v>
@@ -1642,7 +1637,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1651,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593689</v>
+        <v>593688</v>
       </c>
       <c r="R10" t="n">
-        <v>7183537</v>
+        <v>7183529</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1723,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515890</v>
+        <v>121515918</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1739,16 +1734,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1768,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593688</v>
+        <v>593574</v>
       </c>
       <c r="R11" t="n">
-        <v>7183529</v>
+        <v>7183444</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1803,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,7 +1808,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,7 +1835,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515885</v>
+        <v>121515891</v>
       </c>
       <c r="B12" t="n">
         <v>57357</v>
@@ -1885,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593747</v>
+        <v>593657</v>
       </c>
       <c r="R12" t="n">
-        <v>7183470</v>
+        <v>7183534</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1920,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1930,7 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,7 +1952,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515891</v>
+        <v>121515920</v>
       </c>
       <c r="B13" t="n">
         <v>57357</v>
@@ -1993,7 +1988,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2002,10 +1997,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593657</v>
+        <v>593492</v>
       </c>
       <c r="R13" t="n">
-        <v>7183534</v>
+        <v>7183248</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2037,7 +2032,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2047,7 +2042,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,7 +2069,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515893</v>
+        <v>121515882</v>
       </c>
       <c r="B14" t="n">
         <v>57357</v>
@@ -2110,7 +2105,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2119,10 +2114,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593618</v>
+        <v>593762</v>
       </c>
       <c r="R14" t="n">
-        <v>7183571</v>
+        <v>7183468</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2154,7 +2149,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2164,7 +2159,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2191,7 +2186,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515920</v>
+        <v>121515893</v>
       </c>
       <c r="B15" t="n">
         <v>57357</v>
@@ -2227,7 +2222,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2236,10 +2231,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593492</v>
+        <v>593618</v>
       </c>
       <c r="R15" t="n">
-        <v>7183248</v>
+        <v>7183571</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2271,7 +2266,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2281,7 +2276,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2308,10 +2303,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515919</v>
+        <v>121515922</v>
       </c>
       <c r="B16" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2324,34 +2319,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593574</v>
+        <v>593510</v>
       </c>
       <c r="R16" t="n">
-        <v>7183442</v>
+        <v>7183224</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2420,7 +2420,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515883</v>
+        <v>121515892</v>
       </c>
       <c r="B17" t="n">
         <v>57357</v>
@@ -2456,7 +2456,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593756</v>
+        <v>593635</v>
       </c>
       <c r="R17" t="n">
-        <v>7183469</v>
+        <v>7183578</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 38123-2024 artfynd.xlsx
+++ b/artfynd/A 38123-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515889</v>
+        <v>121515884</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593689</v>
+        <v>593756</v>
       </c>
       <c r="R2" t="n">
-        <v>7183537</v>
+        <v>7183462</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515919</v>
+        <v>121515920</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +808,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593574</v>
+        <v>593492</v>
       </c>
       <c r="R3" t="n">
-        <v>7183442</v>
+        <v>7183248</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515888</v>
+        <v>121515889</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -940,7 +945,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -949,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593716</v>
+        <v>593689</v>
       </c>
       <c r="R4" t="n">
-        <v>7183526</v>
+        <v>7183537</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1138,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515885</v>
+        <v>121515890</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1174,7 +1179,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1183,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593747</v>
+        <v>593688</v>
       </c>
       <c r="R6" t="n">
-        <v>7183470</v>
+        <v>7183529</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1218,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,7 +1260,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515884</v>
+        <v>121515885</v>
       </c>
       <c r="B7" t="n">
         <v>57357</v>
@@ -1291,7 +1296,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1300,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593756</v>
+        <v>593747</v>
       </c>
       <c r="R7" t="n">
-        <v>7183462</v>
+        <v>7183470</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1372,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515914</v>
+        <v>121515893</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,34 +1393,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593577</v>
+        <v>593618</v>
       </c>
       <c r="R8" t="n">
-        <v>7183447</v>
+        <v>7183571</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1447,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,7 +1494,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515883</v>
+        <v>121515888</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1529,10 +1539,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593756</v>
+        <v>593716</v>
       </c>
       <c r="R9" t="n">
-        <v>7183469</v>
+        <v>7183526</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1564,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1584,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,7 +1611,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515890</v>
+        <v>121515922</v>
       </c>
       <c r="B10" t="n">
         <v>57357</v>
@@ -1637,7 +1647,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1646,10 +1656,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593688</v>
+        <v>593510</v>
       </c>
       <c r="R10" t="n">
-        <v>7183529</v>
+        <v>7183224</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1681,7 +1691,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1701,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515918</v>
+        <v>121515919</v>
       </c>
       <c r="B11" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,29 +1744,24 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
@@ -1766,7 +1771,7 @@
         <v>593574</v>
       </c>
       <c r="R11" t="n">
-        <v>7183444</v>
+        <v>7183442</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1835,10 +1840,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515891</v>
+        <v>121515914</v>
       </c>
       <c r="B12" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1851,39 +1856,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593657</v>
+        <v>593577</v>
       </c>
       <c r="R12" t="n">
-        <v>7183534</v>
+        <v>7183447</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,7 +1952,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121515920</v>
+        <v>121515891</v>
       </c>
       <c r="B13" t="n">
         <v>57357</v>
@@ -1988,7 +1988,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593492</v>
+        <v>593657</v>
       </c>
       <c r="R13" t="n">
-        <v>7183248</v>
+        <v>7183534</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2069,7 +2069,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121515882</v>
+        <v>121515892</v>
       </c>
       <c r="B14" t="n">
         <v>57357</v>
@@ -2105,7 +2105,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593762</v>
+        <v>593635</v>
       </c>
       <c r="R14" t="n">
-        <v>7183468</v>
+        <v>7183578</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2186,10 +2186,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515893</v>
+        <v>121515918</v>
       </c>
       <c r="B15" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2202,16 +2202,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2222,7 +2222,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593618</v>
+        <v>593574</v>
       </c>
       <c r="R15" t="n">
-        <v>7183571</v>
+        <v>7183444</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2303,7 +2303,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515922</v>
+        <v>121515883</v>
       </c>
       <c r="B16" t="n">
         <v>57357</v>
@@ -2339,7 +2339,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593510</v>
+        <v>593756</v>
       </c>
       <c r="R16" t="n">
-        <v>7183224</v>
+        <v>7183469</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2420,7 +2420,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515892</v>
+        <v>121515882</v>
       </c>
       <c r="B17" t="n">
         <v>57357</v>
@@ -2456,7 +2456,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593635</v>
+        <v>593762</v>
       </c>
       <c r="R17" t="n">
-        <v>7183578</v>
+        <v>7183468</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 38123-2024 artfynd.xlsx
+++ b/artfynd/A 38123-2024 artfynd.xlsx
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515884</v>
+        <v>121515914</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593756</v>
+        <v>593577</v>
       </c>
       <c r="R2" t="n">
-        <v>7183462</v>
+        <v>7183447</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,55 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515920</v>
+        <v>121515919</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593492</v>
+        <v>593574</v>
       </c>
       <c r="R3" t="n">
-        <v>7183248</v>
+        <v>7183442</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,32 +889,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515889</v>
+        <v>121515918</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -945,7 +920,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593689</v>
+        <v>593574</v>
       </c>
       <c r="R4" t="n">
-        <v>7183537</v>
+        <v>7183444</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -989,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,12 +1004,7 @@
         <v>121515881</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,15 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515890</v>
+        <v>121515882</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593688</v>
+        <v>593762</v>
       </c>
       <c r="R6" t="n">
-        <v>7183529</v>
+        <v>7183468</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1223,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,15 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515885</v>
+        <v>121515883</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,7 +1256,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1305,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593747</v>
+        <v>593756</v>
       </c>
       <c r="R7" t="n">
-        <v>7183470</v>
+        <v>7183469</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1340,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,15 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515893</v>
+        <v>121515884</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1368,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1422,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593618</v>
+        <v>593756</v>
       </c>
       <c r="R8" t="n">
-        <v>7183571</v>
+        <v>7183462</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1457,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1422,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,15 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515888</v>
+        <v>121515885</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1480,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1539,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593716</v>
+        <v>593747</v>
       </c>
       <c r="R9" t="n">
-        <v>7183526</v>
+        <v>7183470</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1574,7 +1524,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1534,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,15 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515922</v>
+        <v>121515888</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1592,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1656,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593510</v>
+        <v>593716</v>
       </c>
       <c r="R10" t="n">
-        <v>7183224</v>
+        <v>7183526</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1691,7 +1636,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,7 +1646,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,15 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515919</v>
+        <v>121515889</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,34 +1684,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593574</v>
+        <v>593689</v>
       </c>
       <c r="R11" t="n">
-        <v>7183442</v>
+        <v>7183537</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1803,7 +1748,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,7 +1758,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,15 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515914</v>
+        <v>121515890</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,34 +1796,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593577</v>
+        <v>593688</v>
       </c>
       <c r="R12" t="n">
-        <v>7183447</v>
+        <v>7183529</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1915,7 +1860,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1870,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,12 +1900,7 @@
         <v>121515891</v>
       </c>
       <c r="B13" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2072,12 +2012,7 @@
         <v>121515892</v>
       </c>
       <c r="B14" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2186,15 +2121,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121515918</v>
+        <v>121515893</v>
       </c>
       <c r="B15" t="n">
-        <v>57373</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2202,16 +2132,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2222,7 +2152,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2231,10 +2161,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593574</v>
+        <v>593618</v>
       </c>
       <c r="R15" t="n">
-        <v>7183444</v>
+        <v>7183571</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2266,7 +2196,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2276,7 +2206,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2303,15 +2233,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121515883</v>
+        <v>121515920</v>
       </c>
       <c r="B16" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593756</v>
+        <v>593492</v>
       </c>
       <c r="R16" t="n">
-        <v>7183469</v>
+        <v>7183248</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2383,7 +2308,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2393,7 +2318,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2420,15 +2345,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121515882</v>
+        <v>121515922</v>
       </c>
       <c r="B17" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2456,7 +2376,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2465,10 +2385,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593762</v>
+        <v>593510</v>
       </c>
       <c r="R17" t="n">
-        <v>7183468</v>
+        <v>7183224</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2500,7 +2420,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,7 +2430,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
